--- a/data/trans_bre/P1413-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1413-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,2</t>
+          <t>11,46</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>58,48%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 4,96</t>
+          <t>-2,26; 5,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,14; 13,4</t>
+          <t>5,64; 13,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 9,31</t>
+          <t>2,35; 9,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,02; 15,07</t>
+          <t>7,41; 15,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 38,11</t>
+          <t>-14,22; 40,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,99; 135,37</t>
+          <t>43,98; 137,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,02; 124,41</t>
+          <t>22,19; 122,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,92; 85,87</t>
+          <t>33,34; 88,72</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18,93</t>
+          <t>15,38</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>141,85%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 9,67</t>
+          <t>2,77; 9,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 10,08</t>
+          <t>3,93; 10,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,92; 8,28</t>
+          <t>2,79; 8,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,26; 26,24</t>
+          <t>11,92; 18,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,3; 78,19</t>
+          <t>18,63; 83,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,54; 110,24</t>
+          <t>31,35; 114,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,99; 123,09</t>
+          <t>28,46; 123,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>81,98; 343,32</t>
+          <t>63,62; 125,19</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26,59</t>
+          <t>12,66</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>133,38%</t>
+          <t>63,11%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 10,97</t>
+          <t>1,6; 10,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,27; 11,95</t>
+          <t>5,47; 11,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,99</t>
+          <t>1,39; 7,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,58; 56,98</t>
+          <t>8,62; 16,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,31; 61,89</t>
+          <t>7,08; 59,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,57; 230,86</t>
+          <t>65,73; 231,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,2; 134,95</t>
+          <t>15,41; 133,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,82; 318,94</t>
+          <t>38,46; 97,92</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,61</t>
+          <t>8,79</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>47,41%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 2,48</t>
+          <t>-4,16; 2,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,43; 14,5</t>
+          <t>8,15; 14,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,6; 9,71</t>
+          <t>3,59; 9,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 10,63</t>
+          <t>5,56; 12,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,64; 16,41</t>
+          <t>-22,01; 14,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,0; 215,46</t>
+          <t>87,27; 216,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,56; 125,42</t>
+          <t>32,79; 125,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,26; 62,43</t>
+          <t>26,78; 73,42</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,3</t>
+          <t>12,05</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>64,94%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,84</t>
+          <t>1,32; 4,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,52; 10,88</t>
+          <t>7,64; 10,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,42</t>
+          <t>4,21; 7,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,26; 27,92</t>
+          <t>10,2; 13,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,7; 32,62</t>
+          <t>7,52; 31,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,62; 132,41</t>
+          <t>78,34; 131,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,84; 97,17</t>
+          <t>48,57; 98,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>58,23; 169,73</t>
+          <t>52,31; 80,04</t>
         </is>
       </c>
     </row>
